--- a/public/templates/GrottLuker-Know-Your-Numbers.xlsx
+++ b/public/templates/GrottLuker-Know-Your-Numbers.xlsx
@@ -19,13 +19,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -75,12 +81,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF7D6"/>
+        <fgColor rgb="000F2440"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F2440"/>
+        <fgColor rgb="00FFF7D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -115,22 +121,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -205,6 +224,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1171575" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -496,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -504,448 +553,498 @@
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>POWERED BY  BLUELINE ADVISORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Know Your Numbers</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>A one-page financial snapshot. Round numbers are fine — this is a conversation starter, not a tax return.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Grott Luker &amp; Co. · Client Decision Support Toolkit · platform by BlueLine Advisors</t>
-        </is>
-      </c>
-    </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Yellow cells are yours to fill in. White cells calculate themselves — leave them alone.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Cash &amp; bank accounts</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Investments (non-retirement)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="9" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Retirement accounts</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Real estate</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="9" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Business interests</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Personal property &amp; other</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="11">
         <f>SUM(B7:B12)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Liabilities</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Mortgage</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="9" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Auto loans</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="9" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Student loans</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="9" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="9" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Other debt</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="9" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="11">
         <f>SUM(B16:B20)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Amount (per year)</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Employment income</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="9" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Business / self-employment</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="9" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Investment income</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="9" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Other income</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="9" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Total income</t>
         </is>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="11">
         <f>SUM(B24:B27)</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Amount (per year)</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Housing</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="9" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Living expenses</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="9" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Debt payments</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="8" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Other expenses</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Total expenses</t>
         </is>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="11">
         <f>SUM(B31:B34)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Other figures</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Annual savings &amp; investing</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Life insurance coverage</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="8" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="9" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Disability coverage (monthly benefit)</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="9" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Your snapshot</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr"/>
-      <c r="C42" s="5" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr"/>
+      <c r="C42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Net worth</t>
         </is>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="12">
         <f>B13-B21</f>
         <v/>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>assets − liabilities</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Annual cash flow</t>
         </is>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="12">
         <f>B28-B35</f>
         <v/>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>income − expenses</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>Savings rate</t>
         </is>
       </c>
-      <c r="B45" s="12">
+      <c r="B45" s="14">
         <f>IF(B28&gt;0,B38/B28,0)</f>
         <v/>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="13" t="inlineStr">
         <is>
           <t>annual savings ÷ income</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Debt-to-income</t>
         </is>
       </c>
-      <c r="B46" s="12">
+      <c r="B46" s="14">
         <f>IF(B28&gt;0,B33/B28,0)</f>
         <v/>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>annual debt payments ÷ income</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>When you're done, send this file to Grott Luker &amp; Co. or type the figures into the online form at the link your CPA sent. Educational only; not tax, legal, or investment advice.</t>
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>When you are done, send this file to Grott Luker &amp; Co. or type the figures into the online form at the link your CPA sent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>About Grott Luker &amp; Co.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Certified Public Accountants · Portsmouth, New Hampshire · Accounting | Tax Planning | Advisory. Questions about this log go to your Grott Luker CPA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="16" t="inlineStr"/>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Powered by BlueLine Advisors</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="50" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>The Client Decision Support Toolkit and its templates are built and maintained by BlueLine Advisors, LLC, an SEC-registered investment adviser based in Exeter, NH (registration does not imply any particular level of skill). Using this workbook does not create an advisory relationship with BlueLine. blueline-advisors.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="16" t="inlineStr"/>
+    </row>
+    <row r="56" ht="50" customHeight="1">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Prepared with the Grott Luker &amp; Co. Client Decision Support Toolkit, powered by BlueLine Advisors. This workbook is an educational planning record, not tax, legal, accounting, or investment advice. Figures are the client’s own entries and should be reviewed by Grott Luker &amp; Co. before use in any return or decision.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="10">
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A54:C54"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/templates/GrottLuker-Know-Your-Numbers.xlsx
+++ b/public/templates/GrottLuker-Know-Your-Numbers.xlsx
@@ -9,17 +9,20 @@
   <sheets>
     <sheet name="Know Your Numbers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Know Your Numbers'!$1:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);&quot;–&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,21 +31,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Georgia"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00C9D6E6"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00454650"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
       <b val="1"/>
       <color rgb="000F2440"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="005B6472"/>
+      <color rgb="0026262B"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="000F2440"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -53,23 +71,25 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <color rgb="00726D63"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="000F2440"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
+      <color rgb="00726D63"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="0026262B"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="000F2440"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -86,16 +106,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF7D6"/>
+        <fgColor rgb="00F4F0E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4F0E6"/>
+        <fgColor rgb="00FFFBEA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -104,50 +124,96 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00DDD7C8"/>
+      <bottom style="medium">
+        <color rgb="00C4A054"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00E6E0D2"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="000F2440"/>
+      </top>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00C4A054"/>
       </left>
-      <right style="thin">
-        <color rgb="00DDD7C8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDD7C8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDD7C8"/>
-      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00C4A054"/>
+      </left>
+      <right/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -235,7 +301,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1171575" cy="476250"/>
+    <ext cx="1219200" cy="495300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -543,508 +609,435 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
+    <row r="1" ht="10" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>POWERED BY  BLUELINE ADVISORS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Know Your Numbers</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>A one-page financial snapshot. Round numbers are fine — this is a conversation starter, not a tax return.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Yellow cells are yours to fill in. White cells calculate themselves — leave them alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>A one-page financial snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Round numbers are fine. This is a conversation starter for your meeting with Grott Luker &amp; Co., not a tax return. Light-yellow cells are yours; the snapshot calculates itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>NET WORTH</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>ANNUAL CASH FLOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="6">
+        <f>B19-B27</f>
+        <v/>
+      </c>
+      <c r="D8" s="6">
+        <f>E17-E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>assets − liabilities</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>income − expenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>SAVINGS RATE</t>
+        </is>
+      </c>
+      <c r="B10" s="9">
+        <f>IF(E17&gt;0,E27/E17,0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>DEBT-TO-INCOME</t>
+        </is>
+      </c>
+      <c r="E10" s="9">
+        <f>IF(E17&gt;0,E22/E17,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="10" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="B12" s="11" t="n"/>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>per year</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Cash &amp; bank accounts</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="B13" s="14" t="n"/>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Employment income</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Investments (non-retirement)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="B14" s="14" t="n"/>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Business / self-employment</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Retirement accounts</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="9" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="B15" s="14" t="n"/>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Investment income</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Real estate</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="B16" s="14" t="n"/>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Business interests</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="B17" s="14" t="n"/>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="E17" s="16">
+        <f>SUM(E13:E16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Personal property &amp; other</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="B18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B13" s="11">
-        <f>SUM(B7:B12)</f>
+      <c r="B19" s="16">
+        <f>SUM(B13:B18)</f>
         <v/>
       </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>per year</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Housing</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Liabilities</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="B21" s="11" t="n"/>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Living expenses</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Mortgage</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="9" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="B22" s="14" t="n"/>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Debt payments</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Auto loans</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="9" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="B23" s="14" t="n"/>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Student loans</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="9" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="B24" s="14" t="n"/>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="E24" s="16">
+        <f>SUM(E20:E23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Credit cards</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="B25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Other debt</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="9" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="B26" s="14" t="n"/>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Other figures</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B21" s="11">
-        <f>SUM(B16:B20)</f>
+      <c r="B27" s="16">
+        <f>SUM(B22:B26)</f>
         <v/>
       </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Amount (per year)</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Employment income</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="9" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Business / self-employment</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="9" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Investment income</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="9" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="9" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Total income</t>
-        </is>
-      </c>
-      <c r="B28" s="11">
-        <f>SUM(B24:B27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Amount (per year)</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Housing</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="9" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Living expenses</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="9" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Debt payments</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="9" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Other expenses</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="9" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="B35" s="11">
-        <f>SUM(B31:B34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Other figures</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>Annual savings &amp; investing</t>
         </is>
       </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="9" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="E27" s="14" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Life insurance coverage</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="9" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="E28" s="14" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Disability coverage (monthly benefit)</t>
         </is>
       </c>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="9" t="n"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Your snapshot</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr"/>
-      <c r="C42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>Net worth</t>
-        </is>
-      </c>
-      <c r="B43" s="12">
-        <f>B13-B21</f>
-        <v/>
-      </c>
-      <c r="C43" s="13" t="inlineStr">
-        <is>
-          <t>assets − liabilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>Annual cash flow</t>
-        </is>
-      </c>
-      <c r="B44" s="12">
-        <f>B28-B35</f>
-        <v/>
-      </c>
-      <c r="C44" s="13" t="inlineStr">
-        <is>
-          <t>income − expenses</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Savings rate</t>
-        </is>
-      </c>
-      <c r="B45" s="14">
-        <f>IF(B28&gt;0,B38/B28,0)</f>
-        <v/>
-      </c>
-      <c r="C45" s="13" t="inlineStr">
-        <is>
-          <t>annual savings ÷ income</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>Debt-to-income</t>
-        </is>
-      </c>
-      <c r="B46" s="14">
-        <f>IF(B28&gt;0,B33/B28,0)</f>
-        <v/>
-      </c>
-      <c r="C46" s="13" t="inlineStr">
-        <is>
-          <t>annual debt payments ÷ income</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>When you are done, send this file to Grott Luker &amp; Co. or type the figures into the online form at the link your CPA sent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>About Grott Luker &amp; Co.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>Certified Public Accountants · Portsmouth, New Hampshire · Accounting | Tax Planning | Advisory. Questions about this log go to your Grott Luker CPA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="16" t="inlineStr"/>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>Powered by BlueLine Advisors</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="50" customHeight="1">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t>The Client Decision Support Toolkit and its templates are built and maintained by BlueLine Advisors, LLC, an SEC-registered investment adviser based in Exeter, NH (registration does not imply any particular level of skill). Using this workbook does not create an advisory relationship with BlueLine. blueline-advisors.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="16" t="inlineStr"/>
-    </row>
-    <row r="56" ht="50" customHeight="1">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>Prepared with the Grott Luker &amp; Co. Client Decision Support Toolkit, powered by BlueLine Advisors. This workbook is an educational planning record, not tax, legal, accounting, or investment advice. Figures are the client’s own entries and should be reviewed by Grott Luker &amp; Co. before use in any return or decision.</t>
+      <c r="E29" s="14" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>When you are done</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>Email this file to your Grott Luker CPA, or bring it to the meeting. If you would rather fill it in online, use the link we sent you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Prepared for planning with Grott Luker &amp; Co. This workbook organizes your records; it does not determine what is deductible. Entries are your own; review with your Grott Luker CPA before anything is used in a return or a decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>Grott Luker &amp; Co.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Certified Public Accountants · Portsmouth, New Hampshire · Accounting | Tax Planning | Advisory</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Questions about this workbook go to your Grott Luker CPA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="22" t="inlineStr"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>Prepared for planning with Grott Luker &amp; Co. This workbook organizes your records; it does not determine what is deductible. Entries are your own; review with your Grott Luker CPA before anything is used in a return or a decision.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A52:C52"/>
+  <mergeCells count="14">
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A40:E40"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 Grott Luker &amp; Co. · Know Your Numbers&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/templates/GrottLuker-Know-Your-Numbers.xlsx
+++ b/public/templates/GrottLuker-Know-Your-Numbers.xlsx
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1001,20 +1001,9 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="22" t="inlineStr"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>Prepared for planning with Grott Luker &amp; Co. This workbook organizes your records; it does not determine what is deductible. Entries are your own; review with your Grott Luker CPA before anything is used in a return or a decision.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="12">
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="A7:B7"/>
@@ -1026,7 +1015,6 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A40:E40"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>

--- a/public/templates/GrottLuker-Know-Your-Numbers.xlsx
+++ b/public/templates/GrottLuker-Know-Your-Numbers.xlsx
@@ -154,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -214,6 +214,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -611,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -646,7 +649,7 @@
       <c r="D3" s="1" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>A one-page financial snapshot</t>
+          <t>A one-page financial snapshot   ·   Powered by BlueLine Advisors</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1004,32 @@
         </is>
       </c>
     </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="22" t="inlineStr"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Powered by BlueLine Advisors</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>The Client Decision Support Toolkit and its templates are built and maintained for Grott Luker &amp; Co. by BlueLine Advisors, LLC, an SEC-registered investment adviser in Exeter, NH (registration does not imply any particular level of skill). Using this workbook does not create an advisory relationship with BlueLine.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="15">
     <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A32:E32"/>
@@ -1015,6 +1037,7 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A40:E40"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>

--- a/public/templates/GrottLuker-Know-Your-Numbers.xlsx
+++ b/public/templates/GrottLuker-Know-Your-Numbers.xlsx
@@ -611,6 +611,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F2440"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
